--- a/export.xlsx
+++ b/export.xlsx
@@ -14,21 +14,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>date</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+  <si>
+    <t>Никнейм</t>
+  </si>
+  <si>
+    <t>Психолог</t>
+  </si>
+  <si>
+    <t>Дата консультации</t>
+  </si>
+  <si>
+    <t>Время консультации</t>
+  </si>
+  <si>
+    <t>Дата заполнения</t>
+  </si>
+  <si>
+    <t>Время</t>
   </si>
   <si>
     <t>Zulumuly</t>
@@ -43,7 +46,31 @@
     <t>f</t>
   </si>
   <si>
+    <t>п</t>
+  </si>
+  <si>
+    <t>а</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
     <t>2025-05-04 12:38</t>
+  </si>
+  <si>
+    <t>2025-05-04 17:28</t>
+  </si>
+  <si>
+    <t>2025-05-04 17:33</t>
+  </si>
+  <si>
+    <t>2025-05-04 17:40</t>
+  </si>
+  <si>
+    <t>л</t>
   </si>
 </sst>
 </file>
@@ -401,10 +428,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -420,39 +447,93 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
